--- a/data/sandbox_products_cleaned.xlsx
+++ b/data/sandbox_products_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3203,6 +3203,8746 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Organic Mug Set</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>150.77</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/121</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Advanced Catnip</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/122</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Handcrafted Business Book</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>203.17</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/123</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Ultra Train Set</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>143.16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/124</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Advanced Brooch</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>177.99</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/125</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Classic Wall Art</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/126</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Premium Mystery Novel</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/127</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Flannel Shirt</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/128</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Lightweight Ice Pack</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>191.92</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/129</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Portable Bubble Machine</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/130</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Lightweight Hand Cream</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>188.36</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/131</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Classic Capo</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>105.87</v>
+      </c>
+      <c r="C133" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/132</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Professional Car Charger</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/133</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Sunscreen</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>141.25</v>
+      </c>
+      <c r="C135" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/134</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Portable Chain</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>141.26</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/135</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Advanced Watch</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="C137" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/136</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Modern Stamp Set</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/137</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Limited Edition Pick Set</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/138</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Ultra Slime Kit</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/139</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Portable Essential Oil</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>192.76</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/140</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Limited Edition Melatonin</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>127.15</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/141</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Organic Napkin Holder</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>161.36</v>
+      </c>
+      <c r="C143" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/142</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Belt</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>150.56</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/143</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Organic Self-Help Guide</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="C145" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/144</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Premium Stamp Set</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>193.49</v>
+      </c>
+      <c r="C146" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/145</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Vintage Body Chain</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>126.03</v>
+      </c>
+      <c r="C147" t="n">
+        <v>5</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/146</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Deluxe LED Desk Lamp</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="C148" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/147</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Yoga Mat</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="C149" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/148</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Handcrafted Building Blocks</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>153.64</v>
+      </c>
+      <c r="C150" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/149</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Professional Tablet Stand</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>194.35</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/150</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Vintage Beef Jerky</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>120.07</v>
+      </c>
+      <c r="C152" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/151</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Premium Carving Tools</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/152</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Smart Aquarium Plant</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/153</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Handcrafted Watch</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="C155" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/154</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Vintage Bird Feeder</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="C156" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/155</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Organic Plant Pot</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/156</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Eye Cream</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/157</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Smart Boxing Gloves</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>96.53</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/158</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Portable Tape Dispenser</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/159</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Classic Nail Polish</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/160</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Essential Mystery Novel</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>153.85</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/161</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Premium Omega-3 Capsules</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>201.63</v>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/162</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Classic Leash</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>89.34</v>
+      </c>
+      <c r="C164" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/163</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Essential Stud Earrings</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>158.99</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/164</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Smart Jump Rope</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>150.09</v>
+      </c>
+      <c r="C166" t="n">
+        <v>5</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/165</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Premium History Book</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/166</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Wireless Vinyl Record</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>107.79</v>
+      </c>
+      <c r="C168" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/167</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Advanced Food Bowl</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="C169" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/168</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Professional Hoop Earrings</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="C170" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/169</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Smart Seat Cover</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/170</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Vinyl Record</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="C172" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/171</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Vintage Pull-Up Bar</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>202.91</v>
+      </c>
+      <c r="C173" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/172</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Portable MIDI Controller</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>203.13</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/173</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Advanced Eye Cream</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/174</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Modern Planner</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>113.53</v>
+      </c>
+      <c r="C176" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/175</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Lightweight Chinos</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/176</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Premium Spice Set</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/177</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Handcrafted Phone Mount</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>128.07</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/178</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Professional Sun Shade</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="C180" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/179</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Blood Pressure Monitor</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="C181" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/180</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Deluxe Protein Bar</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>120.78</v>
+      </c>
+      <c r="C182" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/181</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Lightweight Notebook</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>165.84</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/182</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Modern Binder</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>130.68</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/183</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Advanced Car Charger</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="C185" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/184</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Portable Napkin Holder</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>76.76000000000001</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/185</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Professional Leash</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/186</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Deluxe Ice Scraper</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>96.31</v>
+      </c>
+      <c r="C188" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/187</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Vintage Label Maker</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="C189" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/188</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Amp</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>121.82</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/189</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Limited Edition Stuffed Animal</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>149.56</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/190</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Ultra MIDI Controller</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/191</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Classic Watch</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/192</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Modern Children's Book</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="C194" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/193</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Smart Eye Cream</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/194</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Advanced Spice Set</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/195</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Portable Stapler</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/196</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Professional Laptop Sleeve</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>192.64</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/197</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Binder</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/198</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Organic Dollhouse</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>175.94</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/199</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Advanced Stencil Set</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>154.08</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/200</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Compact Metronome</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>160.71</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/201</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Modern Plant Pot</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/202</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Smart Screen Protector</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>173.13</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/203</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Pro Boom Arm</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>142.43</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/204</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Modern Phone Case</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/205</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Smart Popcorn Pack</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="C207" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/206</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Premium Sunglasses</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/207</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Pro Belt</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>144.06</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/208</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Smart Watch</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>168.73</v>
+      </c>
+      <c r="C210" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/209</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Sketchbook</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="C211" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/210</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Premium Ankle Weights</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/211</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Limited Edition Oil Filter</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>112.39</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/212</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Premium Charger</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="C214" t="n">
+        <v>5</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/213</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Limited Edition Wall Art</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>195.03</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/214</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Portable Hair Pin</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/215</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Deluxe Laptop Sleeve</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/216</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Wireless Journal</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/217</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Essential Litter Box</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/218</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Smart Stud Earrings</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/219</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Modern Wiper Blade</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/220</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Portable Tennis Balls</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/221</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Organic Jump Starter</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>204.67</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/222</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Ruler</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/223</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Ultra Face Mask</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>171.32</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/224</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Organic Stapler</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>70.78</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/225</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Pro Desk Organizer</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>101</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/226</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Wireless Steering Wheel Cover</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>156.47</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/227</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Science Book</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>178.14</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/228</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Vintage Sweatband</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="C230" t="n">
+        <v>5</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/229</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Advanced Energy Drink</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/230</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Essential Speaker Cable</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="C232" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/231</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Classic Joggers</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>204.86</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/232</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Classic Water Bottle</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>106.03</v>
+      </c>
+      <c r="C234" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/233</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Wireless Coloring Book</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/234</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Deluxe Pencil Set</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>168.21</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/235</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Handcrafted Joggers</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>117.83</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/236</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Classic Makeup Brush Set</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>149.46</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/237</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Wireless Audio Cable</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/238</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Smart Mouse Pad</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="C240" t="n">
+        <v>4</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/239</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Wireless Chain</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/240</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Lightweight Planner</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/241</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Lightweight Storage Basket</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>174.65</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/242</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Pro Spice Rack</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>184.66</v>
+      </c>
+      <c r="C244" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/243</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Deluxe Bath Bomb</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>79.62</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/244</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Advanced Scarf</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>79.61</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/245</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Portable Popcorn Pack</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="C247" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/246</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Professional HDMI Cable</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/247</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Organic Toe Ring</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>201.23</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/248</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Pro Guitar Strings</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>149.41</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/249</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Essential Sweatband</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>173.68</v>
+      </c>
+      <c r="C251" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/250</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Modern Pet Bed</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>76.45999999999999</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/251</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Lightweight Napkin Holder</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>124.68</v>
+      </c>
+      <c r="C253" t="n">
+        <v>4</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/252</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Resistance Bands</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/253</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Modern Brooch</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/254</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Premium Ring Light</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/255</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Essential Fish Tank Filter</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="C257" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/256</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Brush Kit</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/257</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Compact Throw Pillow</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>194.24</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/258</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Trunk Organizer</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>159.86</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/259</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Body Chain</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/260</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Pro Grooming Brush</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="C262" t="n">
+        <v>5</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/261</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Smart Storage Basket</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>146.35</v>
+      </c>
+      <c r="C263" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/262</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Advanced Olive Oil</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>198.79</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/263</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Professional Stuffed Animal</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>166.62</v>
+      </c>
+      <c r="C265" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/264</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Organic Gaming Mouse</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/265</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Essential LED Desk Lamp</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>156.21</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/266</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Classic Graphic Novel</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>112.38</v>
+      </c>
+      <c r="C268" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/267</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Modern Omega-3 Capsules</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C269" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/268</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Handcrafted Compression Sleeve</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>154.03</v>
+      </c>
+      <c r="C270" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/269</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Lightweight Dog Treat</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>160.82</v>
+      </c>
+      <c r="C271" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/270</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Portable Puzzle Set</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/271</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Compact Travel Guide</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="C273" t="n">
+        <v>5</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/272</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Portable Fitness Tracker</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>147.65</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/273</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Smart Lip Balm</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>117.61</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/274</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Ultra Play Dough</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>60</v>
+      </c>
+      <c r="C276" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/275</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Portable Whiteboard</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="C277" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/276</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Pro Silver Necklace</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>169.56</v>
+      </c>
+      <c r="C278" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/277</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Portable Throw Pillow</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="C279" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/278</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Portable Compression Socks</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="C280" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/279</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Advanced Amp</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>179.11</v>
+      </c>
+      <c r="C281" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/280</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Organic Toner</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="C282" t="n">
+        <v>4</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/281</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Vintage Melatonin</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/282</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Organic Snack Box</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>121.79</v>
+      </c>
+      <c r="C284" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/283</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Classic Snack Box</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="C285" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/284</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Microphone</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C286" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/285</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Wireless Jam Collection</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>107.47</v>
+      </c>
+      <c r="C287" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/286</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Essential Dried Fruit</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/287</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Advanced Flea Collar</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>192.71</v>
+      </c>
+      <c r="C289" t="n">
+        <v>4</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/288</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Portable Mechanical Keyboard</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="C290" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/289</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Deluxe Pasta Set</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/290</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Vintage Honey Jar</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/291</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Classic Body Lotion</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C293" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/292</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Wireless Envelope Pack</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/293</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Chain</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>172.63</v>
+      </c>
+      <c r="C295" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/294</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Hair Oil</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/295</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Organic Wiper Blade</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>201.44</v>
+      </c>
+      <c r="C297" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/296</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Wireless Foam Roller</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>194.7</v>
+      </c>
+      <c r="C298" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/297</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Vintage Calculator</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="C299" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/298</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Smart Science Book</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C300" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/299</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Advanced Calligraphy Set</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="C301" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/300</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Ultra MIDI Controller</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="C302" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/301</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Modern Oil Filter</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>146.29</v>
+      </c>
+      <c r="C303" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/302</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Compact Mouse Pad</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>81.42</v>
+      </c>
+      <c r="C304" t="n">
+        <v>4</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/303</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Pro Vitamin Pack</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>84</v>
+      </c>
+      <c r="C305" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/304</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Portable Stuffed Animal</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/305</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Wireless Joggers</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>181.84</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/306</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Professional Air Freshener</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>148.02</v>
+      </c>
+      <c r="C308" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/307</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Premium Easel</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>125</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/308</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Advanced Stud Earrings</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/309</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Portable Robot Kit</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>107.24</v>
+      </c>
+      <c r="C311" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/310</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Compact Mug Set</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>191.35</v>
+      </c>
+      <c r="C312" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/311</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Essential Science Book</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>130.86</v>
+      </c>
+      <c r="C313" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/312</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Lightweight Biography</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>189.7</v>
+      </c>
+      <c r="C314" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/313</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Organic Eye Cream</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/314</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Premium Omega-3 Capsules</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>115.44</v>
+      </c>
+      <c r="C316" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/315</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Deluxe SSD Drive</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="C317" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/316</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Ultra Bangle</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>194.15</v>
+      </c>
+      <c r="C318" t="n">
+        <v>5</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/317</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Premium Stuffed Animal</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/318</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Vintage Sheet Music</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/319</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Wireless Stapler</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="C321" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/320</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Wireless Food Bowl</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="C322" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/321</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Handcrafted Carving Tools</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>147.17</v>
+      </c>
+      <c r="C323" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/322</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Classic Probiotics</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="C324" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/323</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Dumbbell Set</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="C325" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/324</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Portable Aquarium Plant</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="C326" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/325</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Vintage Table Runner</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/326</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Portable Pop Filter</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>123.12</v>
+      </c>
+      <c r="C328" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/327</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Lightweight Children's Book</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>121.56</v>
+      </c>
+      <c r="C329" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/328</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Gaming Mouse</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="C330" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/329</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Ultra Synthesizer Patch</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>155.11</v>
+      </c>
+      <c r="C331" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/330</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Classic Tape Dispenser</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>176.51</v>
+      </c>
+      <c r="C332" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/331</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Lightweight Coaster Set</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>193.52</v>
+      </c>
+      <c r="C333" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/332</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Trunk Organizer</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="C334" t="n">
+        <v>4</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/333</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Essential Desk Organizer</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>185.73</v>
+      </c>
+      <c r="C335" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/334</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Ultra Spark Plug</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="C336" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/335</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Classic Pendant</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>158.89</v>
+      </c>
+      <c r="C337" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/336</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Vintage Tiara</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>116.86</v>
+      </c>
+      <c r="C338" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/337</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Modern Perfume</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>202.59</v>
+      </c>
+      <c r="C339" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/338</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Professional Color Wheel</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="C340" t="n">
+        <v>4</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/339</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Ultra Wall Art</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>93.41</v>
+      </c>
+      <c r="C341" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/340</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Smart Dumbbell Set</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>147.22</v>
+      </c>
+      <c r="C342" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/341</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Pro Charger</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="C343" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/342</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Portable Business Book</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>192.55</v>
+      </c>
+      <c r="C344" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/343</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Professional Popcorn Pack</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>122.84</v>
+      </c>
+      <c r="C345" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/344</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Deluxe Phone Case</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>110.14</v>
+      </c>
+      <c r="C346" t="n">
+        <v>3</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/345</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Vintage Yoga Mat</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="C347" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/346</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Pro Toner</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>147.87</v>
+      </c>
+      <c r="C348" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/347</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Handcrafted Popcorn Pack</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>123.43</v>
+      </c>
+      <c r="C349" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/348</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Vintage Massage Gun</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>184.15</v>
+      </c>
+      <c r="C350" t="n">
+        <v>3</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/349</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Portable Hoop Earrings</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="C351" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/350</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Wireless Floor Mat</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>88.69</v>
+      </c>
+      <c r="C352" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/351</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Limited Edition Wireless Earbuds</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="C353" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/352</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Limited Edition Charger</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="C354" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/353</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Kite</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>118.29</v>
+      </c>
+      <c r="C355" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/354</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Ultra Bubble Machine</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="C356" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/355</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Smart Bookend</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>151.96</v>
+      </c>
+      <c r="C357" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/356</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Lightweight Sneakers</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>200.94</v>
+      </c>
+      <c r="C358" t="n">
+        <v>4</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/357</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Classic Coconut Water</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>151.61</v>
+      </c>
+      <c r="C359" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/358</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Compact Gaming Mouse</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>146.92</v>
+      </c>
+      <c r="C360" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/359</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Pro Calculator</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>174.36</v>
+      </c>
+      <c r="C361" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/360</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Premium Color Wheel</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>196.92</v>
+      </c>
+      <c r="C362" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/361</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Lightweight Scale</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>184.17</v>
+      </c>
+      <c r="C363" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/362</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Compact Windbreaker</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="C364" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/363</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Essential Moisturizer</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>144.11</v>
+      </c>
+      <c r="C365" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/364</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Modern Marker Pack</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="C366" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/365</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Ultra Label Maker</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="C367" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/366</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Compact Ring Light</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="C368" t="n">
+        <v>4</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/367</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Pro Matcha Powder</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="C369" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/368</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Lightweight Fantasy Epic</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="C370" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/369</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Locket</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>127.92</v>
+      </c>
+      <c r="C371" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/370</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Professional Probiotics</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="C372" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/371</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Compact Bracelet</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="C373" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/372</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Premium Car Charger</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="C374" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/373</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Classic Wireless Earbuds</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>120.91</v>
+      </c>
+      <c r="C375" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/374</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Desk Organizer</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>190.99</v>
+      </c>
+      <c r="C376" t="n">
+        <v>3</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/375</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Handcrafted Vinyl Record</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>163.48</v>
+      </c>
+      <c r="C377" t="n">
+        <v>5</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/376</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Microphone</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="C378" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/377</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Trail Mix</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>105.04</v>
+      </c>
+      <c r="C379" t="n">
+        <v>3</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/378</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Compact Trail Mix</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>203.99</v>
+      </c>
+      <c r="C380" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/379</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Advanced Locket</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>126.47</v>
+      </c>
+      <c r="C381" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/380</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Pet Shampoo</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="C382" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/381</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Essential Scarf</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="C383" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/382</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Smart Drum Sticks</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="C384" t="n">
+        <v>5</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/383</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Lightweight Doormat</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="C385" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/384</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Vintage Slime Kit</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>170.43</v>
+      </c>
+      <c r="C386" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/385</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Modern SSD Drive</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>90.95999999999999</v>
+      </c>
+      <c r="C387" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/386</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Modern Gym Bag</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="C388" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/387</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Advanced Dog Food</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>146.34</v>
+      </c>
+      <c r="C389" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/388</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Compact Sci-Fi Novel</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="C390" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/389</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Limited Edition Grooming Brush</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>187.72</v>
+      </c>
+      <c r="C391" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/390</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Premium Pastel Set</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>176.68</v>
+      </c>
+      <c r="C392" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/391</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Handcrafted Gaming Mouse</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>191.69</v>
+      </c>
+      <c r="C393" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/392</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Collagen Powder</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>126.07</v>
+      </c>
+      <c r="C394" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/393</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Deluxe Catnip</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>95.29000000000001</v>
+      </c>
+      <c r="C395" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/394</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Advanced Zinc Tablets</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="C396" t="n">
+        <v>3</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/395</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Professional Popcorn Pack</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="C397" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/396</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Pro Denim Jacket</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>148.24</v>
+      </c>
+      <c r="C398" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/397</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Lightweight Beanie</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="C399" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/398</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Handcrafted Notebook</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>164.89</v>
+      </c>
+      <c r="C400" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/399</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Limited Edition Bluetooth Speaker</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="C401" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/400</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Professional Flannel Shirt</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>171.02</v>
+      </c>
+      <c r="C402" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/401</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Vintage Marble Run</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="C403" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/402</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Pro Self-Help Guide</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="C404" t="n">
+        <v>4</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/403</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Limited Edition Calculator</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="C405" t="n">
+        <v>5</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/404</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Compact Popcorn Pack</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>168.65</v>
+      </c>
+      <c r="C406" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/405</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Handcrafted Conditioner</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="C407" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/406</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Ultra Cat Tree</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C408" t="n">
+        <v>3</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/407</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Organic Hot Sauce</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>139.44</v>
+      </c>
+      <c r="C409" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/408</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Compact Litter Box</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="C410" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/409</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Wireless Sweatband</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="C411" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/410</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Lightweight Sketchbook</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>116.88</v>
+      </c>
+      <c r="C412" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/411</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Portable Art Portfolio</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>181.73</v>
+      </c>
+      <c r="C413" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/412</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Smart Hot Sauce</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>203.21</v>
+      </c>
+      <c r="C414" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/413</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Limited Edition Dash Cam</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>124.89</v>
+      </c>
+      <c r="C415" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/414</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Portable Exfoliator</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="C416" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/415</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Vintage Scale</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>152.49</v>
+      </c>
+      <c r="C417" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/416</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Lightweight Webcam</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="C418" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/417</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Vintage Towel Set</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>121.47</v>
+      </c>
+      <c r="C419" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/418</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Ultra Pet Carrier</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="C420" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/419</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Dumbbell Set</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="C421" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/420</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Modern Synthesizer Patch</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="C422" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/421</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Pro Music Stand</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>156.18</v>
+      </c>
+      <c r="C423" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/422</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Portable Floor Mat</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="C424" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/423</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Modern Car Charger</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="C425" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/424</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Limited Edition Cat Tree</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>15</v>
+      </c>
+      <c r="C426" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/425</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Advanced Pasta Set</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>182.57</v>
+      </c>
+      <c r="C427" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/426</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Vintage Tennis Balls</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>195.69</v>
+      </c>
+      <c r="C428" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/427</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Vintage Brush Kit</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="C429" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/428</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Handcrafted Skipping Rope</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="C430" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/429</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Tennis Balls</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="C431" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/430</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Classic LED Desk Lamp</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="C432" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/431</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Professional Paint Set</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>146.73</v>
+      </c>
+      <c r="C433" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/432</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Lightweight Chain</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="C434" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/433</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Organic Face Serum</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="C435" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/434</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Limited Edition Label Maker</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="C436" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/435</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Coaster Set</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>148.85</v>
+      </c>
+      <c r="C437" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/436</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Smart Pen Set</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="C438" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/437</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Portable Hoodie</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>189.43</v>
+      </c>
+      <c r="C439" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/438</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Portable Coloring Book</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="C440" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/439</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Lightweight Sunglasses</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="C441" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/440</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Compact Hair Pin</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="C442" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/441</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Eco-Friendly SSD Drive</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="C443" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/442</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Professional Whiteboard</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="C444" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/443</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Classic Skipping Rope</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="C445" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/444</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Pro Dollhouse</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>12</v>
+      </c>
+      <c r="C446" t="n">
+        <v>4</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/445</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Limited Edition Pendant</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="C447" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/446</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Advanced Correction Tape</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="C448" t="n">
+        <v>4</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/447</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Advanced Screen Protector</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>186.81</v>
+      </c>
+      <c r="C449" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/448</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Compact Spark Plug</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>108.04</v>
+      </c>
+      <c r="C450" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/449</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Limited Edition Floor Mat</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>127.16</v>
+      </c>
+      <c r="C451" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/450</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Pro Hoodie</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="C452" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/451</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Portable Ab Wheel</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="C453" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/452</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Pro Ice Scraper</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="C454" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/453</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Handcrafted SSD Drive</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>142.86</v>
+      </c>
+      <c r="C455" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/454</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Classic Tea Collection</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="C456" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/455</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Essential Floor Mat</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>129.18</v>
+      </c>
+      <c r="C457" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/456</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Compact Board Game</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="C458" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/457</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Premium Guitar Strings</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>166.64</v>
+      </c>
+      <c r="C459" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/458</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Compact Olive Oil</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="C460" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/459</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Handcrafted Paint Set</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="C461" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/460</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Vintage Cufflinks</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>175.08</v>
+      </c>
+      <c r="C462" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/461</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Ultra Clock</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>150.28</v>
+      </c>
+      <c r="C463" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/462</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Vintage Coconut Water</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>185.58</v>
+      </c>
+      <c r="C464" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/463</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Smart Pop Filter</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>136.32</v>
+      </c>
+      <c r="C465" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/464</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Portable Calligraphy Set</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="C466" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/465</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Essential Stencil Set</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>72.64</v>
+      </c>
+      <c r="C467" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/466</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Ultra Locket</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>132.16</v>
+      </c>
+      <c r="C468" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/467</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Premium Stencil Set</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="C469" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/468</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Charm</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="C470" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/469</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Lightweight Laptop Sleeve</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>72.93000000000001</v>
+      </c>
+      <c r="C471" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/470</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Compact Ice Scraper</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="C472" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/471</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Picture Frame</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="C473" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/472</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Lightweight Massage Gun</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>152.52</v>
+      </c>
+      <c r="C474" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/473</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Handcrafted Zinc Tablets</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>155.69</v>
+      </c>
+      <c r="C475" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/474</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Fixative Spray</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>199.19</v>
+      </c>
+      <c r="C476" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/475</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Wireless Science Kit</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="C477" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/476</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Organic Polo Shirt</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="C478" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/477</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Compact Gym Bag</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="C479" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/478</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Portable Throw Pillow</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="C480" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/479</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Pro Highlighters</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="C481" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/480</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Premium Action Figure</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>116.38</v>
+      </c>
+      <c r="C482" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/481</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Pro Exfoliator</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="C483" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/482</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Lightweight Throw Pillow</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>170.73</v>
+      </c>
+      <c r="C484" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/483</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Organic Ab Wheel</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="C485" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/484</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Professional Synthesizer Patch</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="C486" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/485</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Smart Monitor Stand</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="C487" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/486</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Classic USB-C Hub</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="C488" t="n">
+        <v>4</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/487</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Beanie</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>121.62</v>
+      </c>
+      <c r="C489" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/488</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Portable Essential Oil</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="C490" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/489</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Ultra Beanie</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="C491" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/490</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Premium Fitness Tracker</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>122.51</v>
+      </c>
+      <c r="C492" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/491</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Smart Tea Collection</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="C493" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/492</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Pro Pendant</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>178.56</v>
+      </c>
+      <c r="C494" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/493</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Essential Hair Oil</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>188.87</v>
+      </c>
+      <c r="C495" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/494</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Wireless Granola</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="C496" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/495</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Advanced Mystery Novel</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="C497" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/496</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Vintage Cat Toy</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="C498" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/497</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Compact Clock</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="C499" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/498</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Gym Bag</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="C500" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/499</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Classic Grooming Brush</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="C501" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://scrapingsandbox.com/product/500</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
